--- a/sheets/대금율보/검수/_목록.xlsx
+++ b/sheets/대금율보/검수/_목록.xlsx
@@ -22335,7 +22335,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 없음. 목차 곡명 '어메징 그레이스'. h = 노라 부호(율명 아래 ― 다음)</t>
+          <t xml:space="preserve">가사 없음. 목차 곡명 '어메징 그레이스'. h = 노라 부호(율명 아래 – 다음)</t>
         </is>
       </c>
     </row>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 없음. 원본 빠르기 □=50. ―‹ = 연음 ― 오른쪽 숨표 &lt;. 1·4줄 2·5줄 같음</t>
+          <t xml:space="preserve">가사 없음. 원본 빠르기 □=50. –‹ = 연음 – 오른쪽 숨표 &lt;. 1·4줄 2·5줄 같음</t>
         </is>
       </c>
     </row>
@@ -23423,7 +23423,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 오른쪽 세로쓰기 아래 '굿거리'. 1줄 9정간 淋 아래 ㄱ(― 없이)</t>
+          <t xml:space="preserve">제목 오른쪽 세로쓰기 아래 '굿거리'. 1줄 9정간 淋 아래 ㄱ(– 없이)</t>
         </is>
       </c>
     </row>
@@ -24203,7 +24203,7 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">원본 湖 모양(氵古)은 㴌. ―ㄱ 은 율명 아래 같은 줄에 ― 와 ㄱ</t>
+          <t xml:space="preserve">원본 湖 모양(氵古)은 㴌. –ㄱ 은 율명 아래 같은 줄에 – 와 ㄱ</t>
         </is>
       </c>
     </row>
@@ -25395,7 +25395,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1줄은 제목 아래 13~16정간만(못갖춘마디·전라도 지리산으로). 2줄 13정간 위 '후렴' 표기 → 2줄 13정간부터 후렴. 정간마다 3분할(칸 안 | 위→아래). 2·3줄 ―ㄱ 은 ― 오른쪽 ㄱ</t>
+          <t xml:space="preserve">1줄은 제목 아래 13~16정간만(못갖춘마디·전라도 지리산으로). 2줄 13정간 위 '후렴' 표기 → 2줄 13정간부터 후렴. 정간마다 3분할(칸 안 | 위→아래). 2·3줄 –ㄱ 은 – 오른쪽 ㄱ</t>
         </is>
       </c>
     </row>
@@ -26475,7 +26475,7 @@
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">원본 연음표가 二(두 줄) 모양으로 인쇄됨 → ―. 율명 사이 가로줄(汰/淋)은 위아래 두 음으로 읽음. 湖 모양은 㴌</t>
+          <t xml:space="preserve">원본 연음표가 二(두 줄) 모양으로 인쇄됨 → –. 율명 사이 가로줄(汰/淋)은 위아래 두 음으로 읽음. 湖 모양은 㴌</t>
         </is>
       </c>
     </row>
@@ -30007,7 +30007,7 @@
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">И = 율명 아래 ― 다음 ㅂ/И 모양 부호(니나 추정). 줄 끝 경계의 &lt; 숨표 일부 생략</t>
+          <t xml:space="preserve">И = 율명 아래 – 다음 ㅂ/И 모양 부호(니나 추정). 줄 끝 경계의 &lt; 숨표 일부 생략</t>
         </is>
       </c>
     </row>
@@ -30367,7 +30367,7 @@
       </c>
       <c r="N158" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">위 단 오른쪽 6줄 → 아래 단 7줄. 6줄 위에 펜 손글씨(가사 덧씀) 있음. 南·汰 오른쪽 ≯ 모양 → ϟ 로 적음 확인 필요. 율명 위 二 모양은 ― 로 적음</t>
+          <t xml:space="preserve">위 단 오른쪽 6줄 → 아래 단 7줄. 6줄 위에 펜 손글씨(가사 덧씀) 있음. 南·汰 오른쪽 ≯ 모양 → ϟ 로 적음 확인 필요. 율명 위 二 모양은 – 로 적음</t>
         </is>
       </c>
     </row>
@@ -31299,7 +31299,7 @@
       </c>
       <c r="N176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1절·2절·후렴(1~20줄) → 3절(21~31) → 세마치 후렴 1~3절(32~55). 1·11줄 가사 없음. 32줄~ 한 소박에 두 음이 나란히 있는 칸은 붙여 씀(淋淋). ―― 는 원본 二 모양(두 반소박 이어짐). ㅂ 는 1줄 칸 아래 모양 그대로</t>
+          <t xml:space="preserve">1절·2절·후렴(1~20줄) → 3절(21~31) → 세마치 후렴 1~3절(32~55). 1·11줄 가사 없음. 32줄~ 한 소박에 두 음이 나란히 있는 칸은 붙여 씀(淋淋). –– 는 원본 二 모양(두 반소박 이어짐). ㅂ 는 1줄 칸 아래 모양 그대로</t>
         </is>
       </c>
     </row>
@@ -31351,7 +31351,7 @@
       </c>
       <c r="N177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 없음. ―‹ = 연음 오른쪽 숨표 &lt;. 2줄 12정간 林 오른쪽 ^ 모양 → ∧(니레)</t>
+          <t xml:space="preserve">가사 없음. –‹ = 연음 오른쪽 숨표 &lt;. 2줄 12정간 林 오른쪽 ^ 모양 → ∧(니레)</t>
         </is>
       </c>
     </row>
@@ -31759,7 +31759,7 @@
       </c>
       <c r="N185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">머리 '잦은모리 빨가장이 노래 / 전주'. 1-2줄 가사 없음 → 전주로 둠(지도는 1:전주). 7줄 8정간 끝 줄. 율명 아래 '―ㄱ' '―ㄴ' 은 한 줄에 나란히 인쇄됨</t>
+          <t xml:space="preserve">머리 '잦은모리 빨가장이 노래 / 전주'. 1-2줄 가사 없음 → 전주로 둠(지도는 1:전주). 7줄 8정간 끝 줄. 율명 아래 '–ㄱ' '–ㄴ' 은 한 줄에 나란히 인쇄됨</t>
         </is>
       </c>
     </row>
@@ -31811,7 +31811,7 @@
       </c>
       <c r="N186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 가로쓰기 '빨강머리 앤 □ = 90'. 율명 아래 ㄱ ㄴ 은 ― 없이 바로 붙음. 5·6줄 같음</t>
+          <t xml:space="preserve">제목 가로쓰기 '빨강머리 앤 □ = 90'. 율명 아래 ㄱ ㄴ 은 – 없이 바로 붙음. 5·6줄 같음</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="N196" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 줄 20정간. 1줄 1정간 위 제목 줄 높이에 못갖춘 시작 칸(汰|―浹 · 가사 천상) — 줄 칸에 넣지 않고 여기와 1줄 1정간 비고에 둠. 沖 모양은 㳞. 율명 옆 작은 점·꾸밈 획은 생략. 숨표 &lt; 는 그 정간 끝 ‹</t>
+          <t xml:space="preserve">한 줄 20정간. 1줄 1정간 위 제목 줄 높이에 못갖춘 시작 칸(汰|–浹 · 가사 천상) — 줄 칸에 넣지 않고 여기와 1줄 1정간 비고에 둠. 沖 모양은 㳞. 율명 옆 작은 점·꾸밈 획은 생략. 숨표 &lt; 는 그 정간 끝 ‹</t>
         </is>
       </c>
     </row>
@@ -32383,7 +32383,7 @@
       </c>
       <c r="N197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 오른쪽 세로쓰기 + 중모리. 머리 1절·후렴·2절·후렴·3절·4절 각 2줄. 나란히 쓴 두 음(林林 등) 아래 ― 는 원본 위치대로. 율명 뒤 , 모양은 ) 흘림. 6정간 끝 숨표 &lt; 는 ‹. 박자 3/4 는 12정간이라 둔 것</t>
+          <t xml:space="preserve">제목 오른쪽 세로쓰기 + 중모리. 머리 1절·후렴·2절·후렴·3절·4절 각 2줄. 나란히 쓴 두 음(林林 등) 아래 – 는 원본 위치대로. 율명 뒤 , 모양은 ) 흘림. 6정간 끝 숨표 &lt; 는 ‹. 박자 3/4 는 12정간이라 둔 것</t>
         </is>
       </c>
     </row>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="N207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1~5절(봄·여름·가을·겨울) 노랫말이 줄마다 이어짐. 아래 단에 잦은모리 표시. 율명 아래 -율명 은 ―율명 으로 적음</t>
+          <t xml:space="preserve">1~5절(봄·여름·가을·겨울) 노랫말이 줄마다 이어짐. 아래 단에 잦은모리 표시. 율명 아래 -율명 은 –율명 으로 적음</t>
         </is>
       </c>
     </row>
@@ -33835,7 +33835,7 @@
       </c>
       <c r="N225" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 오른쪽 세로쓰기. 칸 안 세로 3단(율명|―|율명) 많음</t>
+          <t xml:space="preserve">제목 오른쪽 세로쓰기. 칸 안 세로 3단(율명|–|율명) 많음</t>
         </is>
       </c>
     </row>
@@ -37355,7 +37355,7 @@
       </c>
       <c r="N293" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 없음. 원본 빠르기 □=120. ―‹ = 연음 ― 오른쪽 숨표 &lt;. 율명 옆 작은 점·' 표 생략(1줄). 손글씨: 3줄 8정간 ⊕·6줄 끝 2nd·7줄 9정간 ⊕·7줄 12정간 D.S.⊕</t>
+          <t xml:space="preserve">가사 없음. 원본 빠르기 □=120. –‹ = 연음 – 오른쪽 숨표 &lt;. 율명 옆 작은 점·' 표 생략(1줄). 손글씨: 3줄 8정간 ⊕·6줄 끝 2nd·7줄 9정간 ⊕·7줄 12정간 D.S.⊕</t>
         </is>
       </c>
     </row>
@@ -37979,7 +37979,7 @@
       </c>
       <c r="N305" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 없음. 목차 표기 엽불승. 원본 = 모양(― 두 개)은 ―|― 로 적음</t>
+          <t xml:space="preserve">가사 없음. 목차 표기 엽불승. 원본 = 모양(– 두 개)은 –|– 로 적음</t>
         </is>
       </c>
     </row>
@@ -38031,7 +38031,7 @@
       </c>
       <c r="N306" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 위 가로쓰기 + 세마치. 원본 沖(氵中)은 㳞. ― 오른쪽 작은 &lt; 는 ―‹ 로 적음(뜻 확인 필요). 율명 뒤 , 모양은 ) 흘림. 6정간 끝 숨표 &lt; 는 ‹</t>
+          <t xml:space="preserve">제목 위 가로쓰기 + 세마치. 원본 沖(氵中)은 㳞. – 오른쪽 작은 &lt; 는 –‹ 로 적음(뜻 확인 필요). 율명 뒤 , 모양은 ) 흘림. 6정간 끝 숨표 &lt; 는 ‹</t>
         </is>
       </c>
     </row>
@@ -38963,7 +38963,7 @@
       </c>
       <c r="N324" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">신민요. 원본 滴 모양(氵南)은 湳. 沖 모양은 㳞. ―ㄱ·―ㄴ 은 율명 아래 같은 줄</t>
+          <t xml:space="preserve">신민요. 원본 滴 모양(氵南)은 湳. 沖 모양은 㳞. –ㄱ·–ㄴ 은 율명 아래 같은 줄</t>
         </is>
       </c>
     </row>
@@ -39483,7 +39483,7 @@
       </c>
       <c r="N334" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 오른쪽 세로쓰기 + 중모리. 머리 표기 전주(1줄)·1절(2줄~)·2절(4줄~). 1·3·5줄은 13정간까지만. 원본 沖(氵中)은 㳞. 작은 글씨 세 음(潢無林 등)은 앞꾸밈. ― 오른쪽 작은 &lt; 는 ―‹. 박자 4/4 는 16정간이라 둔 것</t>
+          <t xml:space="preserve">제목 오른쪽 세로쓰기 + 중모리. 머리 표기 전주(1줄)·1절(2줄~)·2절(4줄~). 1·3·5줄은 13정간까지만. 원본 沖(氵中)은 㳞. 작은 글씨 세 음(潢無林 등)은 앞꾸밈. – 오른쪽 작은 &lt; 는 –‹. 박자 4/4 는 16정간이라 둔 것</t>
         </is>
       </c>
     </row>
@@ -40103,7 +40103,7 @@
       </c>
       <c r="N346" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정간마다 3소박(위·가운데·아래). ―㴌 처럼 한 소박 안에 ― 와 율명이 나란히 있음(반소박). 1줄 가사 첫머리 가장자리 잘림. ʒ·∧ 는 율명 오른쪽 꾸밈음. ‹ = 정간 경계 숨표 &lt;</t>
+          <t xml:space="preserve">정간마다 3소박(위·가운데·아래). –㴌 처럼 한 소박 안에 – 와 율명이 나란히 있음(반소박). 1줄 가사 첫머리 가장자리 잘림. ʒ·∧ 는 율명 오른쪽 꾸밈음. ‹ = 정간 경계 숨표 &lt;</t>
         </is>
       </c>
     </row>
@@ -40363,7 +40363,7 @@
       </c>
       <c r="N351" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">원본 沖 모양은 㳞. ―‹ 는 원본 ― 옆 작은 &lt;. 8줄은 8정간까지만 칸이 있음(9~16 빈칸). 汰∧ 는 汰 오른쪽 위 작은 ^ 모양</t>
+          <t xml:space="preserve">원본 沖 모양은 㳞. –‹ 는 원본 – 옆 작은 &lt;. 8줄은 8정간까지만 칸이 있음(9~16 빈칸). 汰∧ 는 汰 오른쪽 위 작은 ^ 모양</t>
         </is>
       </c>
     </row>
@@ -41035,7 +41035,7 @@
       </c>
       <c r="N364" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 오른쪽 세로쓰기 + 세마치. 머리 후렴·1절·2절 각 2줄. 정간 안 율명 사이 ― 는 원본 위치대로. 6정간 끝 숨표 &lt; 는 ‹. 박자 3/4 는 12정간이라 둔 것</t>
+          <t xml:space="preserve">제목 오른쪽 세로쓰기 + 세마치. 머리 후렴·1절·2절 각 2줄. 정간 안 율명 사이 – 는 원본 위치대로. 6정간 끝 숨표 &lt; 는 ‹. 박자 3/4 는 12정간이라 둔 것</t>
         </is>
       </c>
     </row>
@@ -41191,7 +41191,7 @@
       </c>
       <c r="N367" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">男唱 叱音時調(여창 겸용 표기). 한 줄 = 위 단 5정간(5박) + 아래 단 8정간(8박). И 는 율명·― 오른쪽에 붙은 부호 그대로. ⌇ = 칸 오른쪽 물결선(요성). 율명 淸 모양은 湳 · 潏 모양은 㴌 로 읽음</t>
+          <t xml:space="preserve">男唱 叱音時調(여창 겸용 표기). 한 줄 = 위 단 5정간(5박) + 아래 단 8정간(8박). И 는 율명·– 오른쪽에 붙은 부호 그대로. ⌇ = 칸 오른쪽 물결선(요성). 율명 淸 모양은 湳 · 潏 모양은 㴌 로 읽음</t>
         </is>
       </c>
     </row>
@@ -41555,7 +41555,7 @@
       </c>
       <c r="N374" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정간 안 율명 두 줄 배치는 위→아래 높이대로 | 로 적고 같은 높이 둘은 붙여 씀. ―ㄱ 은 ― 오른쪽 ㄱ. 굿거리 표기는 1줄 가사 칸 아래</t>
+          <t xml:space="preserve">정간 안 율명 두 줄 배치는 위→아래 높이대로 | 로 적고 같은 높이 둘은 붙여 씀. –ㄱ 은 – 오른쪽 ㄱ. 굿거리 표기는 1줄 가사 칸 아래</t>
         </is>
       </c>
     </row>
@@ -41867,7 +41867,7 @@
       </c>
       <c r="N380" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">본문 제목 '서편제 中 천년학'. 가사 없음(기악). ― ― △ = 연음 두 번 뒤 쉼</t>
+          <t xml:space="preserve">본문 제목 '서편제 中 천년학'. 가사 없음(기악). – – △ = 연음 두 번 뒤 쉼</t>
         </is>
       </c>
     </row>
@@ -42179,7 +42179,7 @@
       </c>
       <c r="N386" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">청성해탄곡(淸聲解彈曲) 5관청. 요천순일지곡을 5도 아래로 이조해 산조대금 5관청으로 편성(원본 위 설명). 가사 없음. 정간마다 3단. 太·林·南·黃·仲 은 원본 삼수변 없음. 沖(氵中)은 㳞. И 는 율명 오른쪽·― 오른쪽 작은 ч 모양 꾸밈. ⌙ 는 ㄴ 에 갈고리 붙은 모양. ) 는 쉼표 모양 꾸밈. 仲 앞 τ 모양 작은 표시는 ㄱ仲 으로 적음. ʒ 는 3 모양 꾸밈. 9줄은 12정간에서 끝남. 정간 오른쪽 물결선(농음)·&lt; 표시는 옮기지 않음</t>
+          <t xml:space="preserve">청성해탄곡(淸聲解彈曲) 5관청. 요천순일지곡을 5도 아래로 이조해 산조대금 5관청으로 편성(원본 위 설명). 가사 없음. 정간마다 3단. 太·林·南·黃·仲 은 원본 삼수변 없음. 沖(氵中)은 㳞. И 는 율명 오른쪽·– 오른쪽 작은 ч 모양 꾸밈. ⌙ 는 ㄴ 에 갈고리 붙은 모양. ) 는 쉼표 모양 꾸밈. 仲 앞 τ 모양 작은 표시는 ㄱ仲 으로 적음. ʒ 는 3 모양 꾸밈. 9줄은 12정간에서 끝남. 정간 오른쪽 물결선(농음)·&lt; 표시는 옮기지 않음</t>
         </is>
       </c>
     </row>
@@ -43007,7 +43007,7 @@
       </c>
       <c r="N402" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 타령(打令). 가사 없음. 68쪽 위 단 10줄 → 아래 단 10줄 → 69쪽 위 단 10줄 → 69쪽 아래 단 오른쪽 2줄. 장 표시 初章·二章·三章·四章 은 그 줄 오른쪽 좁은 칸. 3정간마다 굵은 선. 빠르기 원본 □=90. 줄 끝 &lt; 숨표는 생략. ― 는 원본 위치대로 다음 글자 위</t>
+          <t xml:space="preserve">제목 타령(打令). 가사 없음. 68쪽 위 단 10줄 → 아래 단 10줄 → 69쪽 위 단 10줄 → 69쪽 아래 단 오른쪽 2줄. 장 표시 初章·二章·三章·四章 은 그 줄 오른쪽 좁은 칸. 3정간마다 굵은 선. 빠르기 원본 □=90. 줄 끝 &lt; 숨표는 생략. – 는 원본 위치대로 다음 글자 위</t>
         </is>
       </c>
     </row>
@@ -43111,7 +43111,7 @@
       </c>
       <c r="N404" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 줄 20정간. 가사 없음. 제목 옆 □=100 Db 無潢(조 표시). И = ― 옆 니나 부호. ʒ = 율명 오른쪽 ч 모양 꾸밈. ) = 오른쪽 아래 흘림 획</t>
+          <t xml:space="preserve">한 줄 20정간. 가사 없음. 제목 옆 □=100 Db 無潢(조 표시). И = – 옆 니나 부호. ʒ = 율명 오른쪽 ч 모양 꾸밈. ) = 오른쪽 아래 흘림 획</t>
         </is>
       </c>
     </row>
@@ -43311,7 +43311,7 @@
       </c>
       <c r="N408" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5정간 ― 아래 ―И (1·2·4줄) 은 ―|―|И 로 적음. 4줄 가사 없음. 汰潢|南 = 위에 汰潢 나란히 아래 南. 1줄 관 글자 위 펜 표시 무시</t>
+          <t xml:space="preserve">5정간 – 아래 –И (1·2·4줄) 은 –|–|И 로 적음. 4줄 가사 없음. 汰潢|南 = 위에 汰潢 나란히 아래 南. 1줄 관 글자 위 펜 표시 무시</t>
         </is>
       </c>
     </row>
@@ -45258,7 +45258,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潕?</t>
         </is>
       </c>
@@ -45295,7 +45295,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 淋潕?</t>
         </is>
       </c>
@@ -45479,7 +45479,7 @@
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰?
-―淋
+–淋
 淋</t>
         </is>
       </c>
@@ -45517,7 +45517,7 @@
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲?
-―
+–
 △</t>
         </is>
       </c>
@@ -45555,7 +45555,7 @@
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲?
-―
+–
 △</t>
         </is>
       </c>
@@ -45593,7 +45593,7 @@
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲?
-―
+–
 △</t>
         </is>
       </c>
@@ -45631,7 +45631,7 @@
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲?
-―
+–
 △</t>
         </is>
       </c>
@@ -45742,7 +45742,7 @@
         <is>
           <t xml:space="preserve">潢?
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -45780,7 +45780,7 @@
         <is>
           <t xml:space="preserve">汰?
 㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -45817,7 +45817,7 @@
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲?
-―
+–
 △</t>
         </is>
       </c>
@@ -46039,7 +46039,7 @@
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 㳞?</t>
         </is>
       </c>
@@ -46077,7 +46077,7 @@
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰?
-―
+–
 㳞</t>
         </is>
       </c>
@@ -46116,7 +46116,7 @@
         <is>
           <t xml:space="preserve">汰
 淋?
-―</t>
+–</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -46154,7 +46154,7 @@
         <is>
           <t xml:space="preserve">汰
 潕?
-―</t>
+–</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -46192,7 +46192,7 @@
         <is>
           <t xml:space="preserve">汰
 淋?
-―</t>
+–</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -46487,7 +46487,7 @@
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞?
-―
+–
 淋</t>
         </is>
       </c>
@@ -46525,7 +46525,7 @@
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 南?</t>
         </is>
       </c>
@@ -46601,7 +46601,7 @@
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 南?</t>
         </is>
       </c>
@@ -46639,7 +46639,7 @@
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲?
-―
+–
 △</t>
         </is>
       </c>
@@ -46677,7 +46677,7 @@
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">淋?
-―
+–
 淋</t>
         </is>
       </c>
@@ -46715,7 +46715,7 @@
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 南?</t>
         </is>
       </c>
@@ -46754,7 +46754,7 @@
         <is>
           <t xml:space="preserve">汰
 淋?
-―</t>
+–</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -46791,7 +46791,7 @@
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潕?
-―
+–
 淋</t>
         </is>
       </c>
@@ -49166,7 +49166,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―)
+          <t xml:space="preserve">–)
 仲?</t>
         </is>
       </c>
@@ -49199,7 +49199,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―)
+          <t xml:space="preserve">–)
 仲?</t>
         </is>
       </c>
@@ -49232,7 +49232,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲?</t>
         </is>
       </c>
@@ -49363,7 +49363,7 @@
         <is>
           <t xml:space="preserve">汰?
 汰
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="H120" s="4"/>
@@ -49397,7 +49397,7 @@
         <is>
           <t xml:space="preserve">林?
 南)
-―</t>
+–</t>
         </is>
       </c>
       <c r="H121" s="4"/>
@@ -49499,7 +49499,7 @@
         <is>
           <t xml:space="preserve">淋?
 淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="H124" s="4"/>
@@ -49533,7 +49533,7 @@
         <is>
           <t xml:space="preserve">淋?
 湳)
-―</t>
+–</t>
         </is>
       </c>
       <c r="H125" s="4"/>
@@ -49567,7 +49567,7 @@
         <is>
           <t xml:space="preserve">汰?
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="H126" s="4"/>
@@ -49700,7 +49700,7 @@
       <c r="G130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
-―
+–
 仲?</t>
         </is>
       </c>
@@ -49735,7 +49735,7 @@
         <is>
           <t xml:space="preserve">南?
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="H131" s="4"/>
@@ -49803,7 +49803,7 @@
         <is>
           <t xml:space="preserve">淋?
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="H133" s="4"/>
@@ -49837,7 +49837,7 @@
         <is>
           <t xml:space="preserve">林
 林?
-―</t>
+–</t>
         </is>
       </c>
       <c r="H134" s="4"/>
@@ -49871,7 +49871,7 @@
         <is>
           <t xml:space="preserve">淋
 淋?
-―</t>
+–</t>
         </is>
       </c>
       <c r="H135" s="4"/>
@@ -50084,7 +50084,7 @@
       <c r="G141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">?仲
-―ㄴ
+–ㄴ
 仲</t>
         </is>
       </c>
@@ -50158,7 +50158,7 @@
       <c r="G143" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">?
-―
+–
 ㄴ
 仲</t>
         </is>
@@ -50197,7 +50197,7 @@
       <c r="G144" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">?
-―
+–
 ㄴ</t>
         </is>
       </c>
@@ -50235,7 +50235,7 @@
       <c r="G145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲?
-―
+–
 ㄴ</t>
         </is>
       </c>
@@ -50741,7 +50741,7 @@
       <c r="G159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南?
-―)
+–)
 南)</t>
         </is>
       </c>
@@ -50780,7 +50780,7 @@
         <is>
           <t xml:space="preserve">林?
 林
-―</t>
+–</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -50856,7 +50856,7 @@
         <is>
           <t xml:space="preserve">林?
 南)
-―</t>
+–</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -50894,7 +50894,7 @@
         <is>
           <t xml:space="preserve">林?
 太
-―</t>
+–</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -50932,7 +50932,7 @@
         <is>
           <t xml:space="preserve">林?
 林
-―</t>
+–</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -50970,7 +50970,7 @@
         <is>
           <t xml:space="preserve">林?
 林
-―</t>
+–</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -51046,7 +51046,7 @@
         <is>
           <t xml:space="preserve">林?
 林
-―</t>
+–</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -51082,7 +51082,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南?</t>
         </is>
       </c>
@@ -51121,7 +51121,7 @@
         <is>
           <t xml:space="preserve">林?
 林
-―太</t>
+–太</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -51159,7 +51159,7 @@
         <is>
           <t xml:space="preserve">林?
 南)
-―</t>
+–</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -51197,7 +51197,7 @@
         <is>
           <t xml:space="preserve">林?
 太
-―</t>
+–</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -51271,7 +51271,7 @@
         <is>
           <t xml:space="preserve">林?
 林
-―</t>
+–</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -51309,7 +51309,7 @@
         <is>
           <t xml:space="preserve">林仲?
 林
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -51345,7 +51345,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 林?
 太</t>
         </is>
@@ -51385,7 +51385,7 @@
         <is>
           <t xml:space="preserve">林?
 林
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -51423,7 +51423,7 @@
         <is>
           <t xml:space="preserve">林?
 太
-―</t>
+–</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -51461,7 +51461,7 @@
         <is>
           <t xml:space="preserve">淋?
 淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -51498,7 +51498,7 @@
       <c r="G179" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">淋?
-―
+–
 △</t>
         </is>
       </c>
@@ -51537,7 +51537,7 @@
         <is>
           <t xml:space="preserve">汰?
 淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -51613,7 +51613,7 @@
         <is>
           <t xml:space="preserve">林?
 林
-―</t>
+–</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -51687,7 +51687,7 @@
         <is>
           <t xml:space="preserve">淋?
 淋
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -51725,7 +51725,7 @@
         <is>
           <t xml:space="preserve">林?
 林
-―
+–
 ㄴ</t>
         </is>
       </c>
@@ -51763,7 +51763,7 @@
       <c r="G186" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―)
+–)
 㳞?</t>
         </is>
       </c>
@@ -51802,7 +51802,7 @@
         <is>
           <t xml:space="preserve">淋?
 淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -51878,7 +51878,7 @@
         <is>
           <t xml:space="preserve">淋?
 淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -51916,7 +51916,7 @@
         <is>
           <t xml:space="preserve">淋?
 淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -51954,7 +51954,7 @@
         <is>
           <t xml:space="preserve">淋?
 淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -51992,7 +51992,7 @@
         <is>
           <t xml:space="preserve">淋?
 淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -52030,7 +52030,7 @@
         <is>
           <t xml:space="preserve">淋?
 淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -52180,7 +52180,7 @@
         <is>
           <t xml:space="preserve">淋?
 淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -52364,7 +52364,7 @@
         <is>
           <t xml:space="preserve">㑣?
 㑣
-―</t>
+–</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -52401,7 +52401,7 @@
       <c r="G203" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南)
-―
+–
 林?</t>
         </is>
       </c>
@@ -52440,7 +52440,7 @@
         <is>
           <t xml:space="preserve">淋?
 淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -52630,7 +52630,7 @@
         <is>
           <t xml:space="preserve">林?
 林
-―</t>
+–</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -52704,7 +52704,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―㳞
+          <t xml:space="preserve">–㳞
 汰?
 㳞</t>
         </is>
@@ -52744,7 +52744,7 @@
         <is>
           <t xml:space="preserve">南?
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -52896,7 +52896,7 @@
         <is>
           <t xml:space="preserve">林?
 林
-―</t>
+–</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -53080,7 +53080,7 @@
         <is>
           <t xml:space="preserve">淋
 汰?
-―</t>
+–</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr">
